--- a/results/exp/experiments.xlsx
+++ b/results/exp/experiments.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="144">
   <si>
     <t>状态</t>
   </si>
@@ -406,6 +406,12 @@
   </si>
   <si>
     <t>收敛</t>
+  </si>
+  <si>
+    <t>未完成(运行83 min后停止)</t>
+  </si>
+  <si>
+    <t>未完成(运行71 min后停止)</t>
   </si>
   <si>
     <t>模型</t>
@@ -7643,7 +7649,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -7838,6 +7844,90 @@
       </c>
       <c r="P4">
         <v>673.3194979260893</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5">
+        <v>4960</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6">
+        <v>193750543.0855362</v>
+      </c>
+      <c r="E6">
+        <v>188549.0592190921</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>18899</v>
+      </c>
+      <c r="H6">
+        <v>28826</v>
+      </c>
+      <c r="I6">
+        <v>1800.295051336288</v>
+      </c>
+      <c r="J6">
+        <v>25</v>
+      </c>
+      <c r="K6">
+        <v>2099</v>
+      </c>
+      <c r="L6">
+        <v>3336.302985664205</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>2583.868685160855</v>
+      </c>
+      <c r="P6">
+        <v>721.2283069920238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7">
+        <v>4258</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7852,28 +7942,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7881,7 +7971,7 @@
         <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C2">
         <v>56</v>
@@ -7907,7 +7997,7 @@
         <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C3">
         <v>56</v>
@@ -7933,7 +8023,7 @@
         <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C4">
         <v>56</v>
@@ -7959,7 +8049,7 @@
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C5">
         <v>56</v>
@@ -7985,7 +8075,7 @@
         <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C6">
         <v>55</v>
@@ -8011,7 +8101,7 @@
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C7">
         <v>55</v>
@@ -8037,7 +8127,7 @@
         <v>95</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C8">
         <v>54</v>
@@ -8063,7 +8153,7 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C9">
         <v>54</v>
@@ -8089,7 +8179,7 @@
         <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C10">
         <v>221</v>

--- a/results/exp/experiments.xlsx
+++ b/results/exp/experiments.xlsx
@@ -207,6 +207,9 @@
     <t>冷却修复_EB</t>
   </si>
   <si>
+    <t>不可安全运行日数</t>
+  </si>
+  <si>
     <t>模式占比_R|k2_浅锁频</t>
   </si>
   <si>
@@ -214,9 +217,6 @@
   </si>
   <si>
     <t>模式占比_B|k3_深锁频</t>
-  </si>
-  <si>
-    <t>不可安全运行日数</t>
   </si>
   <si>
     <t>温区5小时</t>
@@ -1071,13 +1071,13 @@
         <v>6553743.370460837</v>
       </c>
       <c r="W2">
-        <v>5060695.27631591</v>
+        <v>5060697.381864482</v>
       </c>
       <c r="X2">
-        <v>192844565.1607135</v>
+        <v>192844567.2662621</v>
       </c>
       <c r="Y2">
-        <v>6273653.56824581</v>
+        <v>6273655.673794382</v>
       </c>
       <c r="Z2">
         <v>0.989377409760321</v>
@@ -1104,16 +1104,16 @@
         <v>17206.26581273899</v>
       </c>
       <c r="AH2">
-        <v>460.5694447168272</v>
+        <v>460.5547328787781</v>
       </c>
       <c r="AI2">
-        <v>12192.68864474643</v>
+        <v>12192.66640462519</v>
       </c>
       <c r="AJ2">
-        <v>1.230240905528005</v>
+        <v>1.230241520690291</v>
       </c>
       <c r="AK2">
-        <v>0.952863099222942</v>
+        <v>0.9527574423184488</v>
       </c>
       <c r="AL2">
         <v>2757.943549816871</v>
@@ -1191,6 +1191,9 @@
         <v>0</v>
       </c>
       <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
         <v>0</v>
       </c>
     </row>
@@ -1262,13 +1265,13 @@
         <v>6941354.285037062</v>
       </c>
       <c r="W3">
-        <v>5051930.865059017</v>
+        <v>5052064.834957472</v>
       </c>
       <c r="X3">
-        <v>193221088.1344412</v>
+        <v>193221222.1043396</v>
       </c>
       <c r="Y3">
-        <v>6650176.541973501</v>
+        <v>6650310.511871955</v>
       </c>
       <c r="Z3">
         <v>0.999505856395452</v>
@@ -1277,37 +1280,37 @@
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>544.7993326474062</v>
+        <v>544.7993326474071</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>544.7993326474062</v>
+        <v>544.7993326474063</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>7.958078640513122E-13</v>
       </c>
       <c r="AF3">
         <v>0.07368421052631578</v>
       </c>
       <c r="AG3">
-        <v>17191.43992263792</v>
+        <v>17190.55069700991</v>
       </c>
       <c r="AH3">
-        <v>496.3844701057189</v>
+        <v>472.7425168695419</v>
       </c>
       <c r="AI3">
-        <v>12162.4159615324</v>
+        <v>12162.59400506035</v>
       </c>
       <c r="AJ3">
-        <v>1.232894538093637</v>
+        <v>1.231211617796132</v>
       </c>
       <c r="AK3">
-        <v>0.9449492768335829</v>
+        <v>0.9370516716891184</v>
       </c>
       <c r="AL3">
-        <v>2760.670078411727</v>
+        <v>2751.336874076873</v>
       </c>
       <c r="AM3">
         <v>0</v>
@@ -1370,6 +1373,9 @@
         <v>0</v>
       </c>
       <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
         <v>0</v>
       </c>
     </row>
@@ -1441,13 +1447,13 @@
         <v>6736825.300652164</v>
       </c>
       <c r="W4">
-        <v>5079010.723506108</v>
+        <v>5078918.753572524</v>
       </c>
       <c r="X4">
-        <v>193186877.8235214</v>
+        <v>193186785.8535878</v>
       </c>
       <c r="Y4">
-        <v>6615966.231053725</v>
+        <v>6615874.261120141</v>
       </c>
       <c r="Z4">
         <v>0.999505856395452</v>
@@ -1456,37 +1462,37 @@
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>544.799332647407</v>
+        <v>544.7993326474066</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>544.7993326474066</v>
+        <v>544.7993326474065</v>
       </c>
       <c r="AE4">
-        <v>4.547473508864641E-13</v>
+        <v>1.13686837721616E-13</v>
       </c>
       <c r="AF4">
         <v>0.07368421052631578</v>
       </c>
       <c r="AG4">
-        <v>17216.68006047092</v>
+        <v>17215.35130380386</v>
       </c>
       <c r="AH4">
-        <v>494.2020082355413</v>
+        <v>472.0106598582807</v>
       </c>
       <c r="AI4">
-        <v>12254.77630068795</v>
+        <v>12254.14330278135</v>
       </c>
       <c r="AJ4">
-        <v>1.232748729729589</v>
+        <v>1.231157909865528</v>
       </c>
       <c r="AK4">
-        <v>0.9548875271597244</v>
+        <v>0.9480708713708017</v>
       </c>
       <c r="AL4">
-        <v>2758.473944994885</v>
+        <v>2758.473944994886</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -1552,12 +1558,15 @@
         <v>0</v>
       </c>
       <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
         <v>0.7058903885495897</v>
       </c>
-      <c r="BM4">
+      <c r="BN4">
         <v>0.00092813689946264</v>
       </c>
-      <c r="BN4">
+      <c r="BO4">
         <v>0.2371421483714785</v>
       </c>
     </row>
@@ -1629,13 +1638,13 @@
         <v>6865304.663792358</v>
       </c>
       <c r="W5">
-        <v>5060850.730493658</v>
+        <v>5060818.23546912</v>
       </c>
       <c r="X5">
-        <v>193154552.8411593</v>
+        <v>193154520.3461347</v>
       </c>
       <c r="Y5">
-        <v>6583641.248691582</v>
+        <v>6583608.753667044</v>
       </c>
       <c r="Z5">
         <v>0.999505856395452</v>
@@ -1644,37 +1653,37 @@
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>544.7993326474061</v>
+        <v>544.7993326474045</v>
       </c>
       <c r="AC5">
         <v>2.273736754432321E-13</v>
       </c>
       <c r="AD5">
-        <v>544.7993326474057</v>
+        <v>544.7993326474043</v>
       </c>
       <c r="AE5">
-        <v>4.547473508864641E-13</v>
+        <v>2.273736754432321E-13</v>
       </c>
       <c r="AF5">
         <v>0.07368421052631578</v>
       </c>
       <c r="AG5">
-        <v>17217.91859279768</v>
+        <v>17217.27395163411</v>
       </c>
       <c r="AH5">
-        <v>501.4072206004915</v>
+        <v>479.4762756328328</v>
       </c>
       <c r="AI5">
-        <v>12187.47668641367</v>
+        <v>12187.33282218017</v>
       </c>
       <c r="AJ5">
-        <v>1.233275079754972</v>
+        <v>1.231705198822676</v>
       </c>
       <c r="AK5">
-        <v>0.9471654217528076</v>
+        <v>0.940384209644382</v>
       </c>
       <c r="AL5">
-        <v>2752.915590845455</v>
+        <v>2753.050160242776</v>
       </c>
       <c r="AM5">
         <v>1188.958874458875</v>
@@ -1739,7 +1748,7 @@
       <c r="BH5">
         <v>0</v>
       </c>
-      <c r="BO5">
+      <c r="BL5">
         <v>0</v>
       </c>
     </row>
@@ -1811,13 +1820,13 @@
         <v>6579780.33804094</v>
       </c>
       <c r="W6">
-        <v>5076804.338540388</v>
+        <v>5077587.854053233</v>
       </c>
       <c r="X6">
-        <v>193061576.965999</v>
+        <v>193062360.4815118</v>
       </c>
       <c r="Y6">
-        <v>6490665.373531325</v>
+        <v>6491448.889044169</v>
       </c>
       <c r="Z6">
         <v>0.9991154567831111</v>
@@ -1826,16 +1835,16 @@
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>975.2196523915679</v>
+        <v>975.2196523915645</v>
       </c>
       <c r="AC6">
-        <v>5.10702591327572E-15</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>544.7993326474061</v>
+        <v>544.7993326474063</v>
       </c>
       <c r="AE6">
-        <v>430.4203197441618</v>
+        <v>430.4203197441582</v>
       </c>
       <c r="AF6">
         <v>0.08421052631578947</v>
@@ -1844,16 +1853,16 @@
         <v>17212.75763352198</v>
       </c>
       <c r="AH6">
-        <v>479.1660303604021</v>
+        <v>475.3587444927494</v>
       </c>
       <c r="AI6">
-        <v>12246.73017241719</v>
+        <v>12249.11405554358</v>
       </c>
       <c r="AJ6">
-        <v>1.231655548361028</v>
+        <v>1.231408260162674</v>
       </c>
       <c r="AK6">
-        <v>0.9505000399591865</v>
+        <v>0.9472184479439841</v>
       </c>
       <c r="AL6">
         <v>2775.484040472717</v>
@@ -1934,16 +1943,16 @@
         <v>0</v>
       </c>
       <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
         <v>0.7240247035373287</v>
       </c>
-      <c r="BM6">
-        <v>0</v>
-      </c>
       <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
         <v>0.2405637710179546</v>
-      </c>
-      <c r="BO6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:72">
@@ -2085,7 +2094,7 @@
       <c r="AT7">
         <v>0.261416055499001</v>
       </c>
-      <c r="BO7">
+      <c r="BL7">
         <v>0</v>
       </c>
     </row>
@@ -2229,16 +2238,16 @@
         <v>0.02382242049799986</v>
       </c>
       <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
         <v>0.7269685318209085</v>
       </c>
-      <c r="BM8">
+      <c r="BN8">
         <v>2.097594707621696E-06</v>
       </c>
-      <c r="BN8">
+      <c r="BO8">
         <v>0.2405249006572248</v>
-      </c>
-      <c r="BO8">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:72">
@@ -2380,7 +2389,7 @@
       <c r="AT9">
         <v>0.261416055499001</v>
       </c>
-      <c r="BO9">
+      <c r="BL9">
         <v>0</v>
       </c>
     </row>
@@ -2524,16 +2533,16 @@
         <v>0.02382241942338093</v>
       </c>
       <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
         <v>0.7269684990276766</v>
       </c>
-      <c r="BM10">
-        <v>0</v>
-      </c>
       <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
         <v>0.2405270325114265</v>
-      </c>
-      <c r="BO10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:72">
@@ -2604,13 +2613,13 @@
         <v>6771255.250546283</v>
       </c>
       <c r="W11">
-        <v>4732182.191125583</v>
+        <v>4732516.40647607</v>
       </c>
       <c r="X11">
-        <v>179493669.2735765</v>
+        <v>179494003.488927</v>
       </c>
       <c r="Y11">
-        <v>6433371.574417572</v>
+        <v>6433705.78976806</v>
       </c>
       <c r="Z11">
         <v>0.9985407876743061</v>
@@ -2628,25 +2637,25 @@
         <v>1608.799332647405</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>4.547473508864641E-13</v>
       </c>
       <c r="AF11">
         <v>0.07368421052631578</v>
       </c>
       <c r="AG11">
-        <v>16073.52172558749</v>
+        <v>16066.80395739585</v>
       </c>
       <c r="AH11">
-        <v>500.9538052414217</v>
+        <v>469.6412675298875</v>
       </c>
       <c r="AI11">
-        <v>11265.15794163744</v>
+        <v>11265.65212915836</v>
       </c>
       <c r="AJ11">
-        <v>1.236768515329419</v>
+        <v>1.234381518103446</v>
       </c>
       <c r="AK11">
-        <v>0.9453072275367957</v>
+        <v>0.9358577870493259</v>
       </c>
       <c r="AL11">
         <v>2512.118662636277</v>
@@ -2675,7 +2684,7 @@
       <c r="AT11">
         <v>0.2879025164166291</v>
       </c>
-      <c r="BO11">
+      <c r="BL11">
         <v>0</v>
       </c>
     </row>
@@ -2747,13 +2756,13 @@
         <v>6279237.007669268</v>
       </c>
       <c r="W12">
-        <v>4791861.061497638</v>
+        <v>4791829.399631544</v>
       </c>
       <c r="X12">
-        <v>179242400.6323484</v>
+        <v>179242368.9704823</v>
       </c>
       <c r="Y12">
-        <v>6182102.933189491</v>
+        <v>6182071.271323397</v>
       </c>
       <c r="Z12">
         <v>0.998275892636702</v>
@@ -2762,13 +2771,13 @@
         <v>1</v>
       </c>
       <c r="AB12">
-        <v>1900.849332647406</v>
+        <v>1900.849332647407</v>
       </c>
       <c r="AC12">
-        <v>3.979039320256561E-13</v>
+        <v>-1.443078460960394E-12</v>
       </c>
       <c r="AD12">
-        <v>1608.799332647405</v>
+        <v>1608.799332647406</v>
       </c>
       <c r="AE12">
         <v>292.0500000000009</v>
@@ -2780,16 +2789,16 @@
         <v>16140.94300968073</v>
       </c>
       <c r="AH12">
-        <v>435.2337274376849</v>
+        <v>433.6683873413978</v>
       </c>
       <c r="AI12">
-        <v>11491.04360207778</v>
+        <v>11491.02885928739</v>
       </c>
       <c r="AJ12">
-        <v>1.231653186765687</v>
+        <v>1.231570912997544</v>
       </c>
       <c r="AK12">
-        <v>0.9642804279527349</v>
+        <v>0.9614684092756633</v>
       </c>
       <c r="AL12">
         <v>2539.284897012397</v>
@@ -2819,16 +2828,16 @@
         <v>0.02524264100033184</v>
       </c>
       <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
         <v>0.6946496217114745</v>
       </c>
-      <c r="BM12">
+      <c r="BN12">
         <v>0.006064518692239064</v>
       </c>
-      <c r="BN12">
+      <c r="BO12">
         <v>0.2595697159447243</v>
-      </c>
-      <c r="BO12">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:72">
@@ -2970,7 +2979,7 @@
       <c r="AT13">
         <v>0.3102848302629621</v>
       </c>
-      <c r="BO13">
+      <c r="BL13">
         <v>0</v>
       </c>
     </row>
@@ -3042,13 +3051,13 @@
         <v>6755476.504841462</v>
       </c>
       <c r="W14">
-        <v>5057603.080847279</v>
+        <v>5057570.658743096</v>
       </c>
       <c r="X14">
-        <v>193117747.9882465</v>
+        <v>193117715.5661423</v>
       </c>
       <c r="Y14">
-        <v>6546836.395778851</v>
+        <v>6546803.973674667</v>
       </c>
       <c r="Z14">
         <v>0.999505856395452</v>
@@ -3057,34 +3066,34 @@
         <v>1</v>
       </c>
       <c r="AB14">
-        <v>544.7993326474075</v>
+        <v>544.7993326474068</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>-6.434852650727407E-13</v>
       </c>
       <c r="AD14">
-        <v>544.7993326474066</v>
+        <v>544.7993326474063</v>
       </c>
       <c r="AE14">
-        <v>9.094947017729282E-13</v>
+        <v>4.547473508864641E-13</v>
       </c>
       <c r="AF14">
         <v>0.07368421052631578</v>
       </c>
       <c r="AG14">
-        <v>16521.96757531316</v>
+        <v>16522.22812926575</v>
       </c>
       <c r="AH14">
-        <v>476.4455794515239</v>
+        <v>465.0490241061289</v>
       </c>
       <c r="AI14">
-        <v>12106.56271720712</v>
+        <v>12106.54893611308</v>
       </c>
       <c r="AJ14">
-        <v>1.231459681274307</v>
+        <v>1.230646101910842</v>
       </c>
       <c r="AK14">
-        <v>0.9746589859871158</v>
+        <v>0.9708743669476005</v>
       </c>
       <c r="AL14">
         <v>2719.002770679255</v>
@@ -3114,16 +3123,16 @@
         <v>0.005776365097495694</v>
       </c>
       <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
         <v>0.6798643097386595</v>
       </c>
-      <c r="BM14">
+      <c r="BN14">
         <v>0.003440434976799931</v>
       </c>
-      <c r="BN14">
+      <c r="BO14">
         <v>0.3053830076057011</v>
-      </c>
-      <c r="BO14">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:72">
@@ -3194,13 +3203,13 @@
         <v>7112425.368262155</v>
       </c>
       <c r="W15">
-        <v>5432145.597667251</v>
+        <v>5432180.46544864</v>
       </c>
       <c r="X15">
-        <v>193183903.4261699</v>
+        <v>193183938.2939513</v>
       </c>
       <c r="Y15">
-        <v>6612991.83370221</v>
+        <v>6613026.7014836</v>
       </c>
       <c r="Z15">
         <v>0.999505856395452</v>
@@ -3209,16 +3218,16 @@
         <v>1</v>
       </c>
       <c r="AB15">
-        <v>544.7993326474066</v>
+        <v>544.7993326474067</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>-1.4210854715202E-12</v>
       </c>
       <c r="AD15">
         <v>544.7993326474066</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.13686837721616E-13</v>
       </c>
       <c r="AF15">
         <v>0.07368421052631578</v>
@@ -3227,16 +3236,16 @@
         <v>17255.29061951081</v>
       </c>
       <c r="AH15">
-        <v>459.9428329138446</v>
+        <v>460.0138531703656</v>
       </c>
       <c r="AI15">
-        <v>13568.644923965</v>
+        <v>13568.75068193419</v>
       </c>
       <c r="AJ15">
-        <v>1.230270387162639</v>
+        <v>1.230277213528166</v>
       </c>
       <c r="AK15">
-        <v>0.996830564165497</v>
+        <v>0.9966671201646595</v>
       </c>
       <c r="AL15">
         <v>2827.363520200975</v>
@@ -3265,7 +3274,7 @@
       <c r="AT15">
         <v>0.3041501188020037</v>
       </c>
-      <c r="BO15">
+      <c r="BL15">
         <v>0</v>
       </c>
     </row>
@@ -3337,13 +3346,13 @@
         <v>6874371.701500822</v>
       </c>
       <c r="W16">
-        <v>5448465.167694784</v>
+        <v>5449222.844496736</v>
       </c>
       <c r="X16">
-        <v>193150852.8003165</v>
+        <v>193151610.4771184</v>
       </c>
       <c r="Y16">
-        <v>6579941.207848794</v>
+        <v>6580698.884650746</v>
       </c>
       <c r="Z16">
         <v>0.999505856395452</v>
@@ -3352,13 +3361,13 @@
         <v>1</v>
       </c>
       <c r="AB16">
-        <v>544.7993326474062</v>
+        <v>544.7993326474057</v>
       </c>
       <c r="AC16">
-        <v>1.605826582817826E-12</v>
+        <v>1.250555214937776E-12</v>
       </c>
       <c r="AD16">
-        <v>544.7993326474062</v>
+        <v>544.7993326474057</v>
       </c>
       <c r="AE16">
         <v>0</v>
@@ -3370,16 +3379,16 @@
         <v>17270.7829561889</v>
       </c>
       <c r="AH16">
-        <v>464.1177509749822</v>
+        <v>465.850391495969</v>
       </c>
       <c r="AI16">
-        <v>13627.58706832623</v>
+        <v>13629.48705533637</v>
       </c>
       <c r="AJ16">
-        <v>1.230577244700066</v>
+        <v>1.230705833489113</v>
       </c>
       <c r="AK16">
-        <v>0.9974674407372216</v>
+        <v>0.9972767079699145</v>
       </c>
       <c r="AL16">
         <v>2847.609905357521</v>
@@ -3409,16 +3418,16 @@
         <v>0.04934424475246601</v>
       </c>
       <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
         <v>0.6756186869091545</v>
       </c>
-      <c r="BM16">
+      <c r="BN16">
         <v>1.968392213073245E-06</v>
       </c>
-      <c r="BN16">
+      <c r="BO16">
         <v>0.2570516556516868</v>
-      </c>
-      <c r="BO16">
-        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:72">
@@ -3560,7 +3569,7 @@
       <c r="AT17">
         <v>0.1350610687507922</v>
       </c>
-      <c r="BO17">
+      <c r="BL17">
         <v>0</v>
       </c>
     </row>
@@ -3704,16 +3713,16 @@
         <v>0</v>
       </c>
       <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
         <v>0.8600176136768457</v>
       </c>
-      <c r="BM18">
+      <c r="BN18">
         <v>2.039286233246714E-06</v>
       </c>
-      <c r="BN18">
+      <c r="BO18">
         <v>0.1375813344197784</v>
-      </c>
-      <c r="BO18">
-        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:72">
@@ -3784,31 +3793,31 @@
         <v>4305879.656051742</v>
       </c>
       <c r="W19">
-        <v>3255016.786937215</v>
+        <v>3254862.129213259</v>
       </c>
       <c r="X19">
-        <v>111573968.1291792</v>
+        <v>111573813.4714552</v>
       </c>
       <c r="Y19">
-        <v>4111256.306743094</v>
+        <v>4111101.649019137</v>
       </c>
       <c r="Z19">
-        <v>0.9619645409230757</v>
+        <v>0.9619645409230708</v>
       </c>
       <c r="AA19">
         <v>1</v>
       </c>
       <c r="AB19">
-        <v>41934.55613170848</v>
+        <v>41934.55613171386</v>
       </c>
       <c r="AC19">
-        <v>-1.272404404062399E-11</v>
+        <v>2.309263891220326E-14</v>
       </c>
       <c r="AD19">
         <v>32754.50797768404</v>
       </c>
       <c r="AE19">
-        <v>9180.048154024444</v>
+        <v>9180.048154029821</v>
       </c>
       <c r="AF19">
         <v>0.5684210526315789</v>
@@ -3817,16 +3826,16 @@
         <v>11446.35831985461</v>
       </c>
       <c r="AH19">
-        <v>299.7336411391126</v>
+        <v>299.7255384189401</v>
       </c>
       <c r="AI19">
-        <v>7846.148567848165</v>
+        <v>7845.396388013099</v>
       </c>
       <c r="AJ19">
-        <v>1.240574496314887</v>
+        <v>1.240575296279434</v>
       </c>
       <c r="AK19">
-        <v>0.927660375757461</v>
+        <v>0.927796175126677</v>
       </c>
       <c r="AL19">
         <v>1746.697228280786</v>
@@ -3907,12 +3916,15 @@
         <v>0</v>
       </c>
       <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
         <v>0.6195649617078639</v>
       </c>
-      <c r="BM19">
-        <v>0</v>
-      </c>
       <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
         <v>0.3294926511129398</v>
       </c>
     </row>
@@ -4056,16 +4068,16 @@
         <v>0.02797277283770201</v>
       </c>
       <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
         <v>0.6998023597052988</v>
       </c>
-      <c r="BM20">
+      <c r="BN20">
         <v>0.004017368053638294</v>
       </c>
-      <c r="BN20">
+      <c r="BO20">
         <v>0.2449612512121654</v>
-      </c>
-      <c r="BO20">
-        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:72">
@@ -4208,16 +4220,16 @@
         <v>0.02382241942338093</v>
       </c>
       <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
         <v>0.7269684990276766</v>
       </c>
-      <c r="BM21">
-        <v>0</v>
-      </c>
       <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
         <v>0.2405270325114265</v>
-      </c>
-      <c r="BO21">
-        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:72">
@@ -4288,13 +4300,13 @@
         <v>6588545.880120696</v>
       </c>
       <c r="W22">
-        <v>5169888.922290392</v>
+        <v>5169776.786010606</v>
       </c>
       <c r="X22">
-        <v>193046671.9731596</v>
+        <v>193046559.8368798</v>
       </c>
       <c r="Y22">
-        <v>6475760.380691923</v>
+        <v>6475648.244412137</v>
       </c>
       <c r="Z22">
         <v>0.9988575340105496</v>
@@ -4303,16 +4315,16 @@
         <v>1</v>
       </c>
       <c r="AB22">
-        <v>1259.582645401623</v>
+        <v>1259.582645401624</v>
       </c>
       <c r="AC22">
-        <v>2.842170943040401E-13</v>
+        <v>-2.259525899717119E-12</v>
       </c>
       <c r="AD22">
-        <v>544.7993326474061</v>
+        <v>544.7993326474063</v>
       </c>
       <c r="AE22">
-        <v>714.7833127542171</v>
+        <v>714.7833127542174</v>
       </c>
       <c r="AF22">
         <v>0.08421052631578947</v>
@@ -4321,16 +4333,16 @@
         <v>17290.16846279622</v>
       </c>
       <c r="AH22">
-        <v>460.892863919815</v>
+        <v>460.3361149625679</v>
       </c>
       <c r="AI22">
-        <v>12577.49349503486</v>
+        <v>12576.89148890037</v>
       </c>
       <c r="AJ22">
-        <v>1.230329834228163</v>
+        <v>1.230305632510841</v>
       </c>
       <c r="AK22">
-        <v>0.976652134756225</v>
+        <v>0.9754894591579472</v>
       </c>
       <c r="AL22">
         <v>2798.109058686043</v>
@@ -4411,16 +4423,16 @@
         <v>0</v>
       </c>
       <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
         <v>0.725136626939473</v>
       </c>
-      <c r="BM22">
+      <c r="BN22">
         <v>0.0006125319795549989</v>
       </c>
-      <c r="BN22">
+      <c r="BO22">
         <v>0.239927477434828</v>
-      </c>
-      <c r="BO22">
-        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:72">
@@ -4563,16 +4575,16 @@
         <v>0.02383478132336084</v>
       </c>
       <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
         <v>0.7187009963331552</v>
       </c>
-      <c r="BM23">
+      <c r="BN23">
         <v>0.004030700482463265</v>
       </c>
-      <c r="BN23">
+      <c r="BO23">
         <v>0.2365344642839047</v>
-      </c>
-      <c r="BO23">
-        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:72">
@@ -4715,16 +4727,16 @@
         <v>0.02381741337210922</v>
       </c>
       <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
         <v>0.7231402421936877</v>
       </c>
-      <c r="BM24">
+      <c r="BN24">
         <v>0.001794474387535911</v>
       </c>
-      <c r="BN24">
+      <c r="BO24">
         <v>0.2386434228449155</v>
-      </c>
-      <c r="BO24">
-        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:72">
@@ -4795,13 +4807,13 @@
         <v>6590072.026228379</v>
       </c>
       <c r="W25">
-        <v>5044233.960171468</v>
+        <v>5046663.744239032</v>
       </c>
       <c r="X25">
-        <v>193072605.7472014</v>
+        <v>193075035.531269</v>
       </c>
       <c r="Y25">
-        <v>6501694.154733754</v>
+        <v>6504123.938801318</v>
       </c>
       <c r="Z25">
         <v>0.9990989009790141</v>
@@ -4810,13 +4822,13 @@
         <v>1</v>
       </c>
       <c r="AB25">
-        <v>993.4726277219224</v>
+        <v>993.4726277219227</v>
       </c>
       <c r="AC25">
-        <v>4.547473508864641E-13</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>544.7993326474063</v>
+        <v>544.7993326474066</v>
       </c>
       <c r="AE25">
         <v>448.6732950745161</v>
@@ -4825,22 +4837,22 @@
         <v>0.08421052631578947</v>
       </c>
       <c r="AG25">
-        <v>17183.29820994543</v>
+        <v>17183.21225870995</v>
       </c>
       <c r="AH25">
-        <v>480.984425066609</v>
+        <v>481.5879703500462</v>
       </c>
       <c r="AI25">
-        <v>12136.14660075509</v>
+        <v>12142.58225788302</v>
       </c>
       <c r="AJ25">
-        <v>1.231781226691928</v>
+        <v>1.231865896339291</v>
       </c>
       <c r="AK25">
-        <v>0.9376581722224492</v>
+        <v>0.9340870468327711</v>
       </c>
       <c r="AL25">
-        <v>2749.263560328608</v>
+        <v>2766.813560328607</v>
       </c>
       <c r="AM25">
         <v>4446.809090909091</v>
@@ -4918,16 +4930,16 @@
         <v>0</v>
       </c>
       <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
         <v>0.7221983341997172</v>
       </c>
-      <c r="BM25">
+      <c r="BN25">
         <v>0.002102960365108166</v>
       </c>
-      <c r="BN25">
+      <c r="BO25">
         <v>0.2384496668798665</v>
-      </c>
-      <c r="BO25">
-        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:72">
@@ -5070,16 +5082,16 @@
         <v>0.02383381215603863</v>
       </c>
       <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
         <v>0.7186717725903131</v>
       </c>
-      <c r="BM26">
+      <c r="BN26">
         <v>0.002139758573035051</v>
       </c>
-      <c r="BN26">
+      <c r="BO26">
         <v>0.2384562862511642</v>
-      </c>
-      <c r="BO26">
-        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:72">
@@ -5222,16 +5234,16 @@
         <v>0.0238174847033536</v>
       </c>
       <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
         <v>0.723142407940762</v>
       </c>
-      <c r="BM27">
+      <c r="BN27">
         <v>0.001933743535423807</v>
       </c>
-      <c r="BN27">
+      <c r="BO27">
         <v>0.2385018788693998</v>
-      </c>
-      <c r="BO27">
-        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:72">
@@ -5302,13 +5314,13 @@
         <v>6586495.632126822</v>
       </c>
       <c r="W28">
-        <v>5041942.251387668</v>
+        <v>5042567.289981156</v>
       </c>
       <c r="X28">
-        <v>193075101.2805696</v>
+        <v>193075726.3191631</v>
       </c>
       <c r="Y28">
-        <v>6504189.688101959</v>
+        <v>6504814.726695447</v>
       </c>
       <c r="Z28">
         <v>0.9990530430187822</v>
@@ -5317,13 +5329,13 @@
         <v>1</v>
       </c>
       <c r="AB28">
-        <v>1044.031586496234</v>
+        <v>1044.031586496232</v>
       </c>
       <c r="AC28">
-        <v>-4.263256414560601E-14</v>
+        <v>8.526512829121202E-13</v>
       </c>
       <c r="AD28">
-        <v>544.7993326474063</v>
+        <v>544.7993326474045</v>
       </c>
       <c r="AE28">
         <v>499.2322538488277</v>
@@ -5335,16 +5347,16 @@
         <v>17180.54513863385</v>
       </c>
       <c r="AH28">
-        <v>481.461577796823</v>
+        <v>478.3884681320607</v>
       </c>
       <c r="AI28">
-        <v>12128.23197383697</v>
+        <v>12130.25860683618</v>
       </c>
       <c r="AJ28">
-        <v>1.231811463457618</v>
+        <v>1.231626891726017</v>
       </c>
       <c r="AK28">
-        <v>0.9364322570397984</v>
+        <v>0.9329895781396189</v>
       </c>
       <c r="AL28">
         <v>2766.030858744723</v>
@@ -5425,16 +5437,16 @@
         <v>0</v>
       </c>
       <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
         <v>0.7183178941369026</v>
       </c>
-      <c r="BM28">
+      <c r="BN28">
         <v>0.00194313964013066</v>
       </c>
-      <c r="BN28">
+      <c r="BO28">
         <v>0.2386604945460262</v>
-      </c>
-      <c r="BO28">
-        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:72">
@@ -5577,16 +5589,16 @@
         <v>0.02420893094066699</v>
       </c>
       <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
         <v>0.7176883761540463</v>
       </c>
-      <c r="BM29">
+      <c r="BN29">
         <v>0.005848763655056186</v>
       </c>
-      <c r="BN29">
+      <c r="BO29">
         <v>0.2343074903633435</v>
-      </c>
-      <c r="BO29">
-        <v>0</v>
       </c>
       <c r="BP29">
         <v>337.9095238095237</v>
@@ -7370,7 +7382,7 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
@@ -7459,16 +7471,16 @@
         <v>0.4526315789473684</v>
       </c>
       <c r="M2">
-        <v>560.6329177832404</v>
+        <v>558.3018343651587</v>
       </c>
       <c r="N2">
         <v>13614.6249731731</v>
       </c>
       <c r="O2">
-        <v>1.23600830495943</v>
+        <v>1.235855718361413</v>
       </c>
       <c r="P2">
-        <v>0.9513309092748012</v>
+        <v>0.9495340232838118</v>
       </c>
       <c r="Q2">
         <v>2998.129413183641</v>
@@ -7482,13 +7494,13 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>5334838.609162649</v>
+        <v>5334838.60916265</v>
       </c>
       <c r="C3">
         <v>193319611.2366213</v>
       </c>
       <c r="D3">
-        <v>6748699.644153586</v>
+        <v>6748699.644153587</v>
       </c>
       <c r="E3">
         <v>0.9907185355355635</v>
@@ -7506,25 +7518,25 @@
         <v>389.1423804624333</v>
       </c>
       <c r="J3">
-        <v>9843.785051311275</v>
+        <v>9843.785051311281</v>
       </c>
       <c r="K3">
         <v>0.4526315789473684</v>
       </c>
       <c r="M3">
-        <v>545.0266906795899</v>
+        <v>540.822398058037</v>
       </c>
       <c r="N3">
         <v>13200.01634627635</v>
       </c>
       <c r="O3">
-        <v>1.236311162547937</v>
+        <v>1.236031961066895</v>
       </c>
       <c r="P3">
-        <v>0.952239117372246</v>
+        <v>0.9485902244609252</v>
       </c>
       <c r="Q3">
-        <v>2775.484040472718</v>
+        <v>2777.270085681936</v>
       </c>
       <c r="R3" t="s">
         <v>117</v>
@@ -7535,22 +7547,22 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>5223128.687391769</v>
+        <v>5222913.593738685</v>
       </c>
       <c r="C4">
-        <v>193207901.3148504</v>
+        <v>193207686.2211973</v>
       </c>
       <c r="D4">
-        <v>6636989.722382706</v>
+        <v>6636774.628729622</v>
       </c>
       <c r="E4">
-        <v>0.983275739768922</v>
+        <v>0.9832757397689216</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>18438.70026658692</v>
+        <v>18438.70026658728</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -7559,7 +7571,7 @@
         <v>544.7993326474066</v>
       </c>
       <c r="J4">
-        <v>17893.90093393952</v>
+        <v>17893.90093393988</v>
       </c>
       <c r="K4">
         <v>0.1578947368421052</v>
@@ -7568,16 +7580,16 @@
         <v>17747.17191283133</v>
       </c>
       <c r="M4">
-        <v>516.3260787685879</v>
+        <v>509.670420958301</v>
       </c>
       <c r="N4">
-        <v>12640.09136913658</v>
+        <v>12639.38243477253</v>
       </c>
       <c r="O4">
-        <v>1.233037850499549</v>
+        <v>1.232564378402621</v>
       </c>
       <c r="P4">
-        <v>0.9568152131935596</v>
+        <v>0.9553632609960614</v>
       </c>
       <c r="Q4">
         <v>2998.129413183641</v>
@@ -7591,13 +7603,13 @@
         <v>0</v>
       </c>
       <c r="B5">
-        <v>5076804.338540388</v>
+        <v>5077587.854053233</v>
       </c>
       <c r="C5">
-        <v>193061576.9659989</v>
+        <v>193062360.4815118</v>
       </c>
       <c r="D5">
-        <v>6490665.373531325</v>
+        <v>6491448.889044169</v>
       </c>
       <c r="E5">
         <v>0.9991154567831112</v>
@@ -7606,16 +7618,16 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>975.219652391568</v>
+        <v>975.2196523915644</v>
       </c>
       <c r="H5">
-        <v>5.10702591327572E-15</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>544.7993326474061</v>
+        <v>544.7993326474063</v>
       </c>
       <c r="J5">
-        <v>430.4203197441618</v>
+        <v>430.4203197441582</v>
       </c>
       <c r="K5">
         <v>0.0842105263157894</v>
@@ -7624,16 +7636,16 @@
         <v>17212.75763352198</v>
       </c>
       <c r="M5">
-        <v>479.1660303604021</v>
+        <v>475.3587444927494</v>
       </c>
       <c r="N5">
-        <v>12246.73017241719</v>
+        <v>12249.11405554358</v>
       </c>
       <c r="O5">
-        <v>1.231655548361028</v>
+        <v>1.231408260162674</v>
       </c>
       <c r="P5">
-        <v>0.9505000399591864</v>
+        <v>0.947218447943984</v>
       </c>
       <c r="Q5">
         <v>2775.484040472717</v>
